--- a/data/trans_orig/Viv_Temp_insuf-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Viv_Temp_insuf-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38757</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29601</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47874</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32569</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24956</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40264</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40300</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51193</t>
+          <t>41018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>72869</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60376</t>
+          <t>60368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86102</t>
+          <t>84156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82860</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73743</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>92016</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>68,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>71158</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63463</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>78771</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>68,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95665</t>
+          <t>69169</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84772</t>
+          <t>61194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105921</t>
+          <t>76955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>166822</t>
+          <t>152029</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153589</t>
+          <t>139673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179315</t>
+          <t>163461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>103727</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>103727</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>103727</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102212</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102212</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>239691</t>
+          <t>223829</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239691</t>
+          <t>223829</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239691</t>
+          <t>223829</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36111</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27854</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44745</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37153</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>29747</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>44798</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>39,24%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36512</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>30362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45450</t>
+          <t>47115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>73666</t>
+          <t>75407</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62643</t>
+          <t>64030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84796</t>
+          <t>86821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55287</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46653</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>63544</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57528</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>49883</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>60,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>59061</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50123</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67135</t>
+          <t>66184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>116588</t>
+          <t>112537</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105458</t>
+          <t>101123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127611</t>
+          <t>123914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23608</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16592</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30535</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25159</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19195</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31322</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>48,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>33291</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51713</t>
+          <t>50085</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42016</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61826</t>
+          <t>58817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,26%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33333</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26406</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40349</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26702</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20539</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32666</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>51,49%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29327</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44353</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>64001</t>
+          <t>60338</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>51606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73698</t>
+          <t>70252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72831</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>61478</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>86439</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>66885</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>44193</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>82698</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75570</t>
+          <t>62012</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63607</t>
+          <t>51941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90621</t>
+          <t>72672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>142454</t>
+          <t>134843</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113401</t>
+          <t>118256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165055</t>
+          <t>150233</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>129113</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>115505</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>140466</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>150941</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>135128</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>173633</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>69,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>142702</t>
+          <t>116571</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127651</t>
+          <t>105911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154665</t>
+          <t>126642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>293643</t>
+          <t>245685</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271042</t>
+          <t>230295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322696</t>
+          <t>262272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>70309</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>55404</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>82389</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,58%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>59950</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>51034</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>69323</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>50,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>75739</t>
+          <t>59840</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58312</t>
+          <t>51494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89307</t>
+          <t>68471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>135690</t>
+          <t>130148</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113190</t>
+          <t>112858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>145052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>77934</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>65854</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>92839</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>52,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>62,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>59478</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>50105</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>68394</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>49,8%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>41,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>86878</t>
+          <t>58891</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73310</t>
+          <t>50260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104305</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>146355</t>
+          <t>136826</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>130742</t>
+          <t>121922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168855</t>
+          <t>154116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>31096</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>24213</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>38557</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>45,54%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>35,46%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>56,46%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>34225</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>26732</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>41583</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>49,68%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>38,8%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>60,36%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>42755</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>65524</t>
+          <t>66196</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55127</t>
+          <t>56202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76221</t>
+          <t>77226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37191</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>29730</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>44074</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>54,46%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>43,54%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>64,54%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>34670</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>27312</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42163</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>50,32%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>61,2%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40704</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32643</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47835</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>75374</t>
+          <t>72448</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>61418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85771</t>
+          <t>82442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>272711</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>248046</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>295109</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>39,61%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>42,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>368</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>255941</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>221673</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>280497</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>38,99%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>33,77%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>42,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>285974</t>
+          <t>255768</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259654</t>
+          <t>235901</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310084</t>
+          <t>277454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>541915</t>
+          <t>528479</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>500154</t>
+          <t>494197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>578860</t>
+          <t>558852</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>415719</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>393321</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>440384</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>60,39%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>57,13%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>63,97%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>560</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>400477</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>375921</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>434745</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>61,01%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>57,27%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>66,23%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>462308</t>
+          <t>364143</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>438198</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>488628</t>
+          <t>384010</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>862785</t>
+          <t>779862</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>825840</t>
+          <t>749489</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>904546</t>
+          <t>814144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>656418</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>656418</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>656418</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>619911</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>619911</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>619911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1404700</t>
+          <t>1308341</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1404700</t>
+          <t>1308341</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1404700</t>
+          <t>1308341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
